--- a/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -618,7 +618,7 @@
     <t>この画像検査が関連しているEncounterリソース</t>
   </si>
   <si>
-    <t>このImagingStudyが行われるヘルスケアイベント（患者とヘルスケアプロバイダの相互作用など）。</t>
+    <t>このImagingStudyが行われる診療イベント（患者と医療提供者の相互作用など）。</t>
   </si>
   <si>
     <t>これは通常、イベントが発生したEncounterであるが、一部のイベントは、Encounterの正式な完了の前または後に開始される場合があり、それでもそのEncounterのコンテキストに関連付けられている（例：入院前の検査）  
@@ -1014,8 +1014,7 @@
     <t>スタディのイメージングマネージャの説明。実施されたスタディ（コンポーネント）の機関生成の説明または分類。</t>
   </si>
   <si>
-    <t>FHIR文字列のサイズは1MBを超えてはならないことに注意。  
-検査に関するフリーコメント。</t>
+    <t>検査に関するフリーコメント。</t>
   </si>
   <si>
     <t>.text</t>
@@ -1167,8 +1166,7 @@
     <t>シリーズの記述。</t>
   </si>
   <si>
-    <t>FHIR文字列のサイズは1MBを超えてはならないことに注意。  
-シリーズごとにつけられるフリーコメント。</t>
+    <t>シリーズごとにつけられるフリーコメント。</t>
   </si>
   <si>
     <t>CT Surview 180</t>
